--- a/label_studio/data_manager/actions/invoice_compare/statisitcs_template_v1.0.xlsx
+++ b/label_studio/data_manager/actions/invoice_compare/statisitcs_template_v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qinqiang02/colab/codespace/ai/label-studio/label_studio/data_manager/actions/invoice_compare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A3032A-DAB3-5542-9692-25DCF9E47770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CCBF46-3C18-E14A-8F80-052402173C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10013,7 +10013,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10059,6 +10062,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
@@ -10124,7 +10135,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10148,38 +10159,48 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10525,178 +10546,231 @@
     <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="20" t="s">
         <v>1628</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" ht="18">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="A2" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="4" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="18">
-      <c r="A3" s="15" t="s">
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" ht="18">
+      <c r="A3" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="18">
-      <c r="A4" s="15" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="15">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" ht="18">
+      <c r="A4" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="1:4" ht="18">
-      <c r="A5" s="15" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="16" t="e">
+        <f>C4/C3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" ht="18">
+      <c r="A5" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-    </row>
-    <row r="6" spans="1:4" ht="18">
-      <c r="A6" s="15" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="16" t="e">
+        <f>C5/C3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" ht="18">
+      <c r="A6" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-    </row>
-    <row r="7" spans="1:4" ht="18">
-      <c r="A7" s="15" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="17">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" ht="18">
+      <c r="A7" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:4" ht="18">
-      <c r="A8" s="15" t="s">
+      <c r="C7" s="11"/>
+      <c r="D7" s="16" t="e">
+        <f>C7/C6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="8" spans="1:5" ht="18">
+      <c r="A8" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="1:4" ht="18">
-      <c r="A9" s="15" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="16" t="e">
+        <f>C8/C6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5" ht="18">
+      <c r="A9" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-    </row>
-    <row r="10" spans="1:4" ht="18">
-      <c r="A10" s="15" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:5" ht="18">
+      <c r="A10" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="15" t="s">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="13" spans="1:4" ht="18">
-      <c r="A13" s="11" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" ht="18">
+      <c r="A13" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" ht="18">
-      <c r="A14" s="13" t="s">
+      <c r="B13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" ht="18">
+      <c r="A14" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="4" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="36">
-      <c r="A15" s="19" t="s">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" spans="1:5" ht="36">
+      <c r="A15" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="C15" s="20"/>
-    </row>
-    <row r="16" spans="1:4" ht="18">
-      <c r="A16" s="19" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" spans="1:5" ht="18">
+      <c r="A16" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="C16" s="21"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:5" ht="18">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" ht="18">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="20" t="s">
         <v>1629</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:5" ht="18">
       <c r="A21" s="4" t="s">
@@ -10716,70 +10790,83 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="18">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" ht="18">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="1:5" ht="18">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="9" t="s">
         <v>1630</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="10" t="s">
         <v>1630</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="22"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="22"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="18" t="s">
         <v>345</v>
       </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="23"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" ht="18">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7"/>

--- a/label_studio/data_manager/actions/invoice_compare/statisitcs_template_v1.0.xlsx
+++ b/label_studio/data_manager/actions/invoice_compare/statisitcs_template_v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qinqiang02/colab/codespace/ai/label-studio/label_studio/data_manager/actions/invoice_compare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CCBF46-3C18-E14A-8F80-052402173C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9424EF37-677C-F54F-9CA6-EA1AF52BAD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10192,15 +10192,15 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10547,12 +10547,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>1628</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
       <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="18">
@@ -10691,11 +10691,11 @@
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="20"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
     </row>
@@ -10764,13 +10764,13 @@
       <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" ht="18">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1629</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="23"/>
     </row>
     <row r="21" spans="1:5" ht="18">
       <c r="A21" s="4" t="s">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="22"/>
+      <c r="E22" s="20"/>
     </row>
     <row r="23" spans="1:5" ht="18">
       <c r="A23" s="9" t="s">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="22"/>
+      <c r="E23" s="20"/>
     </row>
     <row r="24" spans="1:5" ht="18">
       <c r="A24" s="9" t="s">
@@ -10820,28 +10820,28 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="22"/>
+      <c r="E24" s="20"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="9"/>
       <c r="B25" s="10"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="22"/>
+      <c r="E25" s="20"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="9"/>
       <c r="B26" s="10"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="22"/>
+      <c r="E26" s="20"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="9"/>
       <c r="B27" s="10"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="22"/>
+      <c r="E27" s="20"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="18" t="s">
@@ -10850,7 +10850,7 @@
       <c r="B28" s="19"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="23"/>
+      <c r="E28" s="21"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="9"/>
@@ -10860,11 +10860,11 @@
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" ht="18">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="20"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="22"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
     </row>
